--- a/daily_matches/job_matches_2026-08-13.xlsx
+++ b/daily_matches/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, MLflow, Docker, Kubernetes, Git, Snowflake, Databricks, Hadoop, MongoDB</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, EC2, Kubernetes, Jenkins, Git, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Dataflow, CI/CD, Jenkins, GitHub Actions, Git, BigQuery</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, GCP Vertex AI, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MySQL</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, S3, FastAPI, Docker, CI/CD, Git, Matplotlib</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, S3, FastAPI, Docker, CI/CD, Git, Matplotlib</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, S3, FastAPI, Docker, CI/CD, Git, Matplotlib</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, S3, FastAPI, Docker, CI/CD, Git, Matplotlib</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, S3, FastAPI, Docker, CI/CD, Git, Matplotlib</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, S3, FastAPI, Docker, CI/CD, Git, Matplotlib</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, S3, FastAPI, Docker, CI/CD, Git, Matplotlib</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Application Engineering Architect- Enterprise Software/FA&amp;D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Redshift, Git, Redshift, PySpark, Tableau, Power BI, Quicksight</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e4a981c834a387a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Data Scientist, Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, EC2, FastAPI, Docker, AKS, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, S3, EC2, Redshift, Git, Redshift, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=05b2f58eaae34c09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,151 +972,151 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=608618b1815cca7a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Software Engineer II (Credit)</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c7e33422e1a555a</t>
+          <t>https://www.indeed.com/viewjob?jk=c16c77aae1ce8ed2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, AWS SageMaker, CI/CD, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b7cd0c2b62b936</t>
+          <t>https://www.indeed.com/viewjob?jk=493114ee33ab6c46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Senior IT Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frost</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8869831f5e9107a5</t>
+          <t>https://www.indeed.com/viewjob?jk=387bf0db41dda0bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7536a45c1a693b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer- Agentic AI Solutions</t>
+          <t>Applied ML Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+          <t>S3, EC2, Redshift, Git, Redshift, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c7151d5d725957</t>
+          <t>https://www.indeed.com/viewjob?jk=7dde3232c690b9e7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Insights Consultant</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Power BI, SQL, R</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68922026b04aa9e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dce0615b84398da9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, PostgreSQL, Power BI, Python, SQL</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=0c5479d606c4a8e8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8ca723db12b376</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Enterprise AI DevOps SRE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Kafka, MySQL, MongoDB, NoSQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=0af6bf8b671480c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, Agentforce Reasoning</t>
+          <t>AI Developer - Forward Deployed Engineer - Houston, TX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Flight Centre Travel Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, Kafka, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af544c887d36163a</t>
+          <t>https://www.indeed.com/viewjob?jk=747c48f0190263d6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Applied Data Scientist - Personalization (applied ML, PyTorch, ML Ops)</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,777 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff30c9b008af59</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PRADCO</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, XGBoost, YOLO, AWS SageMaker, MLflow, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a96a66a63c39b80b</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Experimentation Data Scientist</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Releady</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Databricks, PySpark, Tableau, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5c6b26533dd91</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior DevOps Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Faith Technologies Incorporated</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Menasha, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Kafka, Hadoop, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81cff073185154b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Hallmark</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, CI/CD, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=697aa02158b0c543</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94ebaac67a9c2b6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Full-Stack Engineer, Internal Tools</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39415ff3c33d7c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer - Infrastructure Automation</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AI Engineer, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=118269c383e31f4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer - Infrastructure Automation</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AI Engineer, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e296f030124dee</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer - Infrastructure Automation</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AI Engineer, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44d39d0981732a18</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer (Job ID 3021693)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f988632f097474a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Sr. DevOps AWS – United States</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>DISTILLERY</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3535f85c629d570</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Agentic Data Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, LLaMA, Copilot, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1735db3bce16b8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer in Test (SET)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Ingram Micro</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Greer, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dca4bf3b3a81310a</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer in Test (SET)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Ingram Micro</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Greer, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6eee3eac4a9a64</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Storage Control Plane</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Lambda</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fba42d31e500244a</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Storage Control Plane</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Lambda</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cffa0e22e43bdd28</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Storage Control Plane</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Lambda</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6bac6c22a75fc182</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Viasat</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Carlsbad, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff86433676d264ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Verizon</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Basking Ridge, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, BigQuery, BigQuery, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=068fe99be7280612</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI Training Sr. Consultant - Developer &amp; End User Enablement</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=001a25758a5610eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Software Engineer (Java/Spring Boot)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Bellwood</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, MongoDB, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98aeff7ba80024af</t>
+          <t>https://www.indeed.com/viewjob?jk=853da5a3c3fdb779</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-13.xlsx
+++ b/daily_matches/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Junior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TensorOps</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, EC2, Kubernetes, Jenkins, Git, MongoDB, Cassandra</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, PyTorch, LightGBM, CatBoost, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=b521419e02507c75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Gemini, Copilot, CI/CD, Git, Kafka, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Applied AI / AWS Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=2cea28c6af921270</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Associate Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3c6c37f4bd02e6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Nuuly Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Nuuly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=60bae50c540c0272</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Boot Barn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=c117b192bfa55f26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Developer - Good Sam AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Camping World</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,637 +741,427 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=55a020f94c8282a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Specialist, Cybersecurity (Full Stack)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9f3df67a527af7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0118b7340485f6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>SPX Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Elk Grove Village, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Git, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=5befbb55fde2495f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Application Engineering Architect- Enterprise Software/FA&amp;D</t>
+          <t>Data Analytics Analyst 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Exton, PA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e4a981c834a387a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c626125e11146</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist, Full Stack</t>
+          <t>Senior Associate - AI Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Redshift, Git, Redshift, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Hugging Face, Git, Databricks, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b2f58eaae34c09</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9cf89bd11da40d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Machine Learning Research Engineer - Central Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sherman Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, PyTorch, XGBoost, AKS, PySpark, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608618b1815cca7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6093ddb4ebb2c911</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Computational Physicist – Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Sciotex</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>TensorFlow, PyTorch, OpenCV, Git, Python, R, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c16c77aae1ce8ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e3c0cd0ef37f26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Solution Engineer – FedRAMP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Coralogix</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493114ee33ab6c46</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb0808c2555f9f3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior IT Data Scientist</t>
+          <t>Solution Engineer – FedRAMP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Coralogix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387bf0db41dda0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4429c5d36e18153a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
+          <t>Solution Engineer – FedRAMP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Coralogix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7536a45c1a693b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb8f0f7c170d62d1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Applied ML Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>BS TECH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, EC2, Redshift, Git, Redshift, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dde3232c690b9e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dce0615b84398da9</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5479d606c4a8e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Earth City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8ca723db12b376</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Enterprise AI DevOps SRE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Trimble</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0af6bf8b671480c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Developer - Forward Deployed Engineer - Houston, TX</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Flight Centre Travel Group</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=747c48f0190263d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=853da5a3c3fdb779</t>
+          <t>https://www.indeed.com/viewjob?jk=85311c69346ac31f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-13.xlsx
+++ b/daily_matches/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer</t>
+          <t>Senior Technical Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TensorOps</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, PyTorch, LightGBM, CatBoost, MLflow, FastAPI, Docker</t>
+          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b521419e02507c75</t>
+          <t>https://www.indeed.com/viewjob?jk=59109dfc565f4f4e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Senior Technical Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b66593bb55d6baa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Technical Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, CI/CD, Git, Kafka, MySQL, NoSQL, Python, SQL</t>
+          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8bbbd004a99070</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI / AWS Engineer II</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,147 +591,147 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Lake, Kubernetes, CI/CD, Git, Databricks, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cea28c6af921270</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Full Stack Developer</t>
+          <t>Associate Power BI and Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Dataflow, Git, Tableau, Power BI, MicroStrategy, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3c6c37f4bd02e6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb100bf934e97393</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nuuly Senior Software Engineer</t>
+          <t>Associate Power BI and Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nuuly</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Dataflow, Git, Tableau, Power BI, MicroStrategy, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bae50c540c0272</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0d1a6ecd7a3a67</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boot Barn</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c117b192bfa55f26</t>
+          <t>https://www.indeed.com/viewjob?jk=4e9d1292a960e249</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Developer - Good Sam AI</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camping World</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,427 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a020f94c8282a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Specialist, Cybersecurity (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Nationwide Mutual Insurance Company</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9f3df67a527af7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Viasat</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Carlsbad, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0118b7340485f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Implementation Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SPX Technologies</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Elk Grove Village, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5befbb55fde2495f</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Analytics Analyst 1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BLOC Resources, LLC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c626125e11146</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Associate - AI Analyst</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Hugging Face, Git, Databricks, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9cf89bd11da40d</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Machine Learning Research Engineer - Central Technology</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Activision</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Sherman Oaks, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, XGBoost, AKS, PySpark, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6093ddb4ebb2c911</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Computational Physicist – Scientific Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Sciotex</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, Git, Python, R, Scala, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e3c0cd0ef37f26</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Solution Engineer – FedRAMP</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Coralogix</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb0808c2555f9f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Solution Engineer – FedRAMP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Coralogix</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4429c5d36e18153a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Solution Engineer – FedRAMP</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Coralogix</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb8f0f7c170d62d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BS TECH</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85311c69346ac31f</t>
+          <t>https://www.indeed.com/viewjob?jk=88ef9526766f0b3a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-13.xlsx
+++ b/daily_matches/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Technical Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Terraform, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59109dfc565f4f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=96db8f9c763bb4ee</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Technical Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
+          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Polars, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b66593bb55d6baa</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Technical Data &amp; AI Enablement Analyst - Legal, Compliance &amp; Policy Org</t>
+          <t>Azure Platform Senior Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, Athena, BigQuery, Data Lake, Git, Databricks, BigQuery, Tableau</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8bbbd004a99070</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Lake, Kubernetes, CI/CD, Git, Databricks, Kafka, Python, R, Java, Scala</t>
+          <t>Snowflake, Kafka, Hadoop, PostgreSQL, MySQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,182 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Associate Power BI and Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Dataflow, Git, Tableau, Power BI, MicroStrategy, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb100bf934e97393</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Associate Power BI and Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Dataflow, Git, Tableau, Power BI, MicroStrategy, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0d1a6ecd7a3a67</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e9d1292a960e249</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sargent &amp; Lundy</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88ef9526766f0b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-13.xlsx
+++ b/daily_matches/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Terraform, NoSQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96db8f9c763bb4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SR. Machine Learning Engineer, Enterprise AI Systems</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Polars, Python, R</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, CI/CD, BigQuery, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=e35d350539d803f6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Platform Senior Engineer</t>
+          <t>Software Engineer II (Marketplace)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Immuta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Snowflake, Databricks, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,287 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=18b1ac655bb4726e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI / Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee22307680d57130</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rubicon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, MLflow, Docker, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Digital Charter, Inc</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, BigQuery, Kafka, MongoDB, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f0d56159c462725</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Platform Engineer - US</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Adarga</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbf173770b138bdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Finance of America</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Python, R, Julia, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cbb45a96403ed58</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a7359a36b66a907</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Technician</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Snowflake, Kafka, Hadoop, PostgreSQL, MySQL, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff617cf7531c6801</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-13.xlsx
+++ b/daily_matches/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery</t>
+          <t>Data Scientist, RAG, FastAPI, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SR. Machine Learning Engineer, Enterprise AI Systems</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, CI/CD, BigQuery, NoSQL, Python</t>
+          <t>Data Scientist, RAG, FastAPI, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35d350539d803f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II (Marketplace)</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Immuta</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Snowflake, Databricks, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Redshift, BigQuery, Apache Airflow, Git, Snowflake, BigQuery, Redshift, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b1ac655bb4726e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI / Machine Learning Engineer II</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Kubernetes, CI/CD, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee22307680d57130</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3c0de0821df9e2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analyst - Business Analytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, Docker, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ca49554b4ebd95</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Analyst - Business Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=0546d7816e8914bb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analyst - Business Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Terraform, BigQuery, Kafka, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0d56159c462725</t>
+          <t>https://www.indeed.com/viewjob?jk=4661437b0a8695e7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Platform Engineer - US</t>
+          <t>Senior Analyst - Business Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adarga</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf173770b138bdd</t>
+          <t>https://www.indeed.com/viewjob?jk=1c5f547b63fc7139</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Analyst - Business Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Python, R, Julia, Scala</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cbb45a96403ed58</t>
+          <t>https://www.indeed.com/viewjob?jk=691cbe69ae7ec701</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analyst - Business Analytics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,1652 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7359a36b66a907</t>
+          <t>https://www.indeed.com/viewjob?jk=4986682191b6b73f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edaaafcfb7f5a605</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=135a04ee6bdd0d5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49bb3436587538d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b361589e1c660a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66a2d1da176d75c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46cbda8784a3e043</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfd866fd6835b857</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bbd186e3e3e053f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d7417b325462e7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=132bf412bf03ed37</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a7f920715c344af</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac487edec200d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cde8f1161fc1ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df2dd488e4d076d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43caaa021c77a453</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a44b1740046a02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e750ba6a7d3c5aa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df5cdfc834713e60</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dfe944808b020b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5047a05a9df7c31e</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0492323754adf0cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b35144048144bb4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4becae3a66db32c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bb1a147a74ce624</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b541220c9cf97f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54369d1e31beff43</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=320aa709905ca016</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54cf359574171a1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=193480a17934acb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8539afb385323575</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=709547c062fff29b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73a4c23f1f796153</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=170f2e97660718a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74468c7806461527</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=799f60204f87f37d</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6071e16de34e6922</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9eb5b3a8191f35f</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4c724b795724e80</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a1e6368996ab6a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49ad8db6cef148ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e5ac87cf3ad0746</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d45ab6ee8f4fae8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ddf2c70ccac0ec7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8857d82d160bd77b</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Senior Software Technician</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Chicago, IL, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D56" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff617cf7531c6801</t>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=369e515e4afd79b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DevOps Enablement Engineer &amp; AI Adoption Specialist</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afbd79c4d6b6a33f</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DevOps Enablement Engineer &amp; AI Adoption Specialist</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06ace55cba750e2e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-13.xlsx
+++ b/daily_matches/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Arity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>RAG, Athena, Redshift, BigQuery, Kubernetes, Apache Airflow, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>AI/Data Science Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Apache Airflow, Git, Snowflake, BigQuery, Redshift, PostgreSQL, MySQL</t>
+          <t>Data Scientist, RAG, FastAPI, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Kubernetes, CI/CD, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3c0de0821df9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ca49554b4ebd95</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0546d7816e8914bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4661437b0a8695e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c5f547b63fc7139</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691cbe69ae7ec701</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4986682191b6b73f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Overseas Contractor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, Azure ML, MLflow, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaaafcfb7f5a605</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2cf0c213693874</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=135a04ee6bdd0d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bb3436587538d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Terraform, Snowflake, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b361589e1c660a3</t>
+          <t>https://www.indeed.com/viewjob?jk=878d3824262f3896</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Power BI, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a2d1da176d75c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, FastAPI, CI/CD, Terraform, Snowflake, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cbda8784a3e043</t>
+          <t>https://www.indeed.com/viewjob?jk=80ff28496adb3397</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Sr. Salesforce Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd866fd6835b857</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbd186e3e3e053f</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb8c1e222fa4dc8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior System Integration Engineer - Enterprise Transformation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7417b325462e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a9742bd7c6e882</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior AI Workflow Engineer - Enterprise Transformation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Gemini, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132bf412bf03ed37</t>
+          <t>https://www.indeed.com/viewjob?jk=2213f793af5121b6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Software Engineer (Fullstack)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f920715c344af</t>
+          <t>https://www.indeed.com/viewjob?jk=8d65873e3282d4a0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Data Scientist (GenAI Solutions) - Hybrid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>XPO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac487edec200d</t>
+          <t>https://www.indeed.com/viewjob?jk=82ec27746de6a161</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Data Scientist (GenAI Solutions) - Hybrid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>XPO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cde8f1161fc1ece</t>
+          <t>https://www.indeed.com/viewjob?jk=55874b8389fe6b40</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, MySQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2dd488e4d076d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55091a3a0eb5d3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Software Engineer, Web Development</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Communify</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43caaa021c77a453</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9af40c795db10c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Software Developer / Senior Software Developer (C# / .NET)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Persante Health Care, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a44b1740046a02</t>
+          <t>https://www.indeed.com/viewjob?jk=53e71fad2ba53db8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e750ba6a7d3c5aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=b03ec566f856aa20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior AI Systems Performance Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Dataflow, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df5cdfc834713e60</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc4244eb02259bb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, NoSQL, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dfe944808b020b5</t>
+          <t>https://www.indeed.com/viewjob?jk=40d2fc9f20aaf219</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Solutions Architect, Adobe Experience Cloud</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5047a05a9df7c31e</t>
+          <t>https://www.indeed.com/viewjob?jk=e49a05090b23585b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0492323754adf0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e02651c1df002e38</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Digital Product Owner - Rental Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35144048144bb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=382d02d17a844d8a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Software Engineer- Backend (Platform)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Yoodli AI Roleplays</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Kubernetes, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4becae3a66db32c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d52b04eded6cecf5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Full Stack Software Engineer (Components)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb1a147a74ce624</t>
+          <t>https://www.indeed.com/viewjob?jk=ec250eb56f86942b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Salesforce Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Rancho Belago, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b541220c9cf97f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1dfef210aa78b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Senior Salesforce Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54369d1e31beff43</t>
+          <t>https://www.indeed.com/viewjob?jk=c08455bffd353ac8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Data Lake, Dataflow, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,707 +1756,77 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320aa709905ca016</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Cloud Platform Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cf359574171a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=40ee12ea08b6cff9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Analytics</t>
+          <t>Cloud Platform Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193480a17934acb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8539afb385323575</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=709547c062fff29b</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73a4c23f1f796153</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CT, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=170f2e97660718a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74468c7806461527</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=799f60204f87f37d</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6071e16de34e6922</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>MT, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9eb5b3a8191f35f</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c724b795724e80</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a1e6368996ab6a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>VT, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49ad8db6cef148ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5ac87cf3ad0746</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>NE, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d45ab6ee8f4fae8</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddf2c70ccac0ec7</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Analytics</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>SD, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8857d82d160bd77b</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Software Technician</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=369e515e4afd79b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>DevOps Enablement Engineer &amp; AI Adoption Specialist</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd79c4d6b6a33f</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>DevOps Enablement Engineer &amp; AI Adoption Specialist</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06ace55cba750e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=d72832f873e04e76</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-13.xlsx
+++ b/daily_matches/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arity</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>40</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Athena, Redshift, BigQuery, Kubernetes, Apache Airflow, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
+          <t>https://www.indeed.com/viewjob?jk=22e1c75da6c86a08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>40</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b609663c97ff4ea</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>40</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=debc4a58840e5d41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, XGBoost, AWS SageMaker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, Glue, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, Glue, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, Glue, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
+          <t>RAG, TensorFlow, EC2, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=9dae9c278d8d7389</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>AI &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Township of Lawrence, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL</t>
+          <t>RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
+          <t>https://www.indeed.com/viewjob?jk=577a4b89164ce0ee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, Azure ML, MLflow, CI/CD, Git, Databricks, Python</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2cf0c213693874</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed3b3fbe175a19b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Copilot, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=48a71fbfbb0ec795</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ML/AI Engineer (Full Time; Multiple Openings)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>RingCentral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>Belmont, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Azure ML, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ed42aa8697ee86</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Terraform, Snowflake, Kafka, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878d3824262f3896</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Power BI, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FastAPI, CI/CD, Terraform, Snowflake, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Snowflake, BigQuery, PostgreSQL, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ff28496adb3397</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f95c888e8fb28a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R</t>
+          <t>RAG, Cortex, FastAPI, Docker, CI/CD, Terraform, Snowflake, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
+          <t>https://www.indeed.com/viewjob?jk=103b7bc10e59d10f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb8c1e222fa4dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior System Integration Engineer - Enterprise Transformation</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, Databricks, BigQuery, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a9742bd7c6e882</t>
+          <t>https://www.indeed.com/viewjob?jk=d0941fcdda00218a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Workflow Engineer - Enterprise Transformation</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Gemini, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213f793af5121b6</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Fullstack)</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quantum Health</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Data Lake, FastAPI, Kafka, PostgreSQL, MySQL, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d65873e3282d4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (GenAI Solutions) - Hybrid</t>
+          <t>AI Data Scientist Precision Oncology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XPO</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ec27746de6a161</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48622bce214ccd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist (GenAI Solutions) - Hybrid</t>
+          <t>AI Data Scientist Precision Oncology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XPO</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55874b8389fe6b40</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6d4993b01cd814</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, MySQL, MongoDB, SQL, R, Java</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Databricks, PySpark, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55091a3a0eb5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Web Development</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Communify</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9af40c795db10c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Developer / Senior Software Developer (C# / .NET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Persante Health Care, Inc.</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,277 +1371,277 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e71fad2ba53db8</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, AKS, CI/CD, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03ec566f856aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Systems Performance Engineer</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Dataflow, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, AKS, CI/CD, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc4244eb02259bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, NoSQL, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>Data Scientist, Generative AI, RAG, AKS, CI/CD, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40d2fc9f20aaf219</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solutions Architect, Adobe Experience Cloud</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, AKS, CI/CD, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49a05090b23585b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, AKS, CI/CD, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02651c1df002e38</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Digital Product Owner - Rental Data</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, AKS, CI/CD, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=382d02d17a844d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Backend (Platform)</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Yoodli AI Roleplays</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kubernetes, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, AKS, CI/CD, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52b04eded6cecf5</t>
+          <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Components)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hawthorne, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec250eb56f86942b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0e2f763e8b2cca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Salesforce Engineer</t>
+          <t>Graduate (Year-Round) Intern - Transportation Systems Analysis</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rancho Belago, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, Git, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1dfef210aa78b</t>
+          <t>https://www.indeed.com/viewjob?jk=5de5897ff18d99ef</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Salesforce Engineer</t>
+          <t>Wi-Fi Infrastructure Test Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08455bffd353ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea407876059774</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>MHC Kenworth</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Dataflow, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=3812773c470dc770</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect</t>
+          <t>Machine Learning Engineer, DesignX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ee12ea08b6cff9</t>
+          <t>https://www.indeed.com/viewjob?jk=feb5e0e789524bb6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,262 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72832f873e04e76</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sales Engineer, DevOps</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Keeper Security, Inc.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec852b1865b5fdff</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Infrastructure as Code Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Corewell Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3952a26268a66b0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Automation Engineer (Marketing)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tax Relief Advocates</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22ac64ef8880a869</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Platform Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, MongoDB, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08df6016a3579aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f69461dfb5de59ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Scientist I, Tech</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59dc2b7d09b0541f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Suzano</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pine Bluff, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc874a97b3504cd0</t>
         </is>
       </c>
     </row>
